--- a/docs/fattibilità/Gantt.xlsx
+++ b/docs/fattibilità/Gantt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gcomi\Desktop\psyPlatform\docs\fattibilità\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{650BCB04-A28E-4FEC-AD67-61173E72D47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853E4104-3F99-4B5B-AF5E-E737FC75ED0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9327F8D6-4F37-4E25-8083-20A17765DC2F}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
   <si>
     <t>TASK</t>
   </si>
@@ -58,19 +58,7 @@
     <t>Month</t>
   </si>
   <si>
-    <t xml:space="preserve">  Task 2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Task 2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Task 2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Task 2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Task 3.1</t>
+    <t xml:space="preserve">  Task 1.4</t>
   </si>
   <si>
     <t xml:space="preserve">  Task 3.2</t>
@@ -118,6 +106,9 @@
     <t>C</t>
   </si>
   <si>
+    <t>Project Start: 6 October 2025</t>
+  </si>
+  <si>
     <t>Gantt v1.0.0</t>
   </si>
   <si>
@@ -154,25 +145,40 @@
     <t>PsyPlatform</t>
   </si>
   <si>
+    <t xml:space="preserve">  Creazione idea progetto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Creazione pagina inziale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Creazione databese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Creazione login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Completamento sito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Documentazione iniziale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Creazione requirements</t>
+  </si>
+  <si>
+    <t>A, B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Zoom con fisioterapista</t>
+  </si>
+  <si>
+    <t>A,B</t>
+  </si>
+  <si>
     <t>Giorgio Cominelli</t>
   </si>
   <si>
     <t>Simone Scainelli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Task 1.1 Creazione pagina iniziale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Task 1.2 Creazione database</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Task 1.3 Creazione form login</t>
-  </si>
-  <si>
-    <t>Project Start: 6 November 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Task 1.4 Create the documentation</t>
   </si>
 </sst>
 </file>
@@ -491,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -664,6 +670,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1049,7 +1058,7 @@
   <cols>
     <col min="1" max="1" width="2.36328125" customWidth="1"/>
     <col min="2" max="2" width="6.08984375" customWidth="1"/>
-    <col min="3" max="3" width="41.36328125" customWidth="1"/>
+    <col min="3" max="3" width="25.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.1796875" customWidth="1"/>
     <col min="5" max="5" width="9.453125" customWidth="1"/>
     <col min="6" max="6" width="10.453125" customWidth="1"/>
@@ -1061,14 +1070,14 @@
   <sheetData>
     <row r="2" spans="3:47" ht="27" customHeight="1">
       <c r="C2" s="62" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D2" s="62"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="3:47">
       <c r="C3" s="61" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D3" s="61"/>
       <c r="H3" s="15" t="s">
@@ -1139,7 +1148,7 @@
     </row>
     <row r="4" spans="3:47">
       <c r="C4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>3</v>
@@ -1252,7 +1261,7 @@
     </row>
     <row r="5" spans="3:47">
       <c r="H5" s="17" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I5" s="11">
         <v>45936</v>
@@ -1360,13 +1369,13 @@
         <v>46174</v>
       </c>
       <c r="AS5" s="49" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="AT5" s="53" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="AU5" s="50" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="3:47" ht="21" customHeight="1">
@@ -1374,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F6" s="37" t="s">
         <v>1</v>
@@ -1427,7 +1436,7 @@
     </row>
     <row r="7" spans="3:47" ht="25" customHeight="1">
       <c r="C7" s="34" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D7" s="34"/>
       <c r="E7" s="28"/>
@@ -1475,24 +1484,24 @@
     </row>
     <row r="8" spans="3:47" ht="21" customHeight="1">
       <c r="C8" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>23</v>
+        <v>34</v>
+      </c>
+      <c r="D8" s="65" t="s">
+        <v>41</v>
       </c>
       <c r="E8" s="27">
         <v>1</v>
       </c>
       <c r="F8" s="30">
-        <v>45969</v>
+        <v>45936</v>
       </c>
       <c r="G8" s="30">
-        <v>45970</v>
+        <v>45939</v>
       </c>
       <c r="H8" s="25"/>
       <c r="I8" s="25">
         <f>1*AND(I$5&gt;=task_start,I$5&lt;=task_start+(task_progress*(task_end-task_start+1))-1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="25"/>
       <c r="K8" s="25"/>
@@ -1543,19 +1552,19 @@
     </row>
     <row r="9" spans="3:47" ht="21" customHeight="1">
       <c r="C9" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>22</v>
+        <v>39</v>
+      </c>
+      <c r="D9" s="65" t="s">
+        <v>18</v>
       </c>
       <c r="E9" s="27">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F9" s="30">
-        <v>45969</v>
+        <v>45940</v>
       </c>
       <c r="G9" s="30">
-        <v>46053</v>
+        <v>45943</v>
       </c>
       <c r="H9" s="24"/>
       <c r="I9" s="25"/>
@@ -1595,32 +1604,32 @@
       <c r="AQ9" s="23"/>
       <c r="AS9" s="8">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AT9" s="54">
         <f t="shared" ref="AT9:AT26" si="1">AS9*$D$36</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AU9" s="56">
         <f t="shared" ref="AU9:AU26" si="2">AT9*$D$37</f>
-        <v>540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="3:47" ht="21" customHeight="1">
       <c r="C10" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>23</v>
+        <v>40</v>
+      </c>
+      <c r="D10" s="65" t="s">
+        <v>18</v>
       </c>
       <c r="E10" s="27">
         <v>1</v>
       </c>
       <c r="F10" s="30">
-        <v>45969</v>
+        <v>45947</v>
       </c>
       <c r="G10" s="30">
-        <v>45973</v>
+        <v>45950</v>
       </c>
       <c r="H10" s="24"/>
       <c r="I10" s="25"/>
@@ -1673,19 +1682,17 @@
     </row>
     <row r="11" spans="3:47" ht="21" customHeight="1">
       <c r="C11" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="27">
-        <v>0.5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D11" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="27"/>
       <c r="F11" s="30">
         <v>45955</v>
       </c>
       <c r="G11" s="30">
-        <v>46173</v>
+        <v>45961</v>
       </c>
       <c r="H11" s="24"/>
       <c r="I11" s="25"/>
@@ -1725,20 +1732,20 @@
       <c r="AQ11" s="23"/>
       <c r="AS11" s="8">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AT11" s="54">
         <f t="shared" si="1"/>
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="AU11" s="56">
         <f t="shared" si="2"/>
-        <v>1395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="3:47" ht="25" customHeight="1">
       <c r="C12" s="35" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D12" s="35"/>
       <c r="E12" s="31"/>
@@ -1795,15 +1802,19 @@
     </row>
     <row r="13" spans="3:47" ht="21" customHeight="1">
       <c r="C13" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="26"/>
+        <v>35</v>
+      </c>
+      <c r="D13" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="27">
+        <v>1</v>
+      </c>
       <c r="F13" s="30">
-        <v>45945</v>
+        <v>45941</v>
       </c>
       <c r="G13" s="30">
-        <v>46022</v>
+        <v>45943</v>
       </c>
       <c r="H13" s="24"/>
       <c r="I13" s="25"/>
@@ -1843,28 +1854,32 @@
       <c r="AQ13" s="23"/>
       <c r="AS13" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AT13" s="54">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AU13" s="56">
         <f t="shared" si="2"/>
-        <v>495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="3:47" ht="21" customHeight="1">
       <c r="C14" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="26"/>
+        <v>36</v>
+      </c>
+      <c r="D14" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="27">
+        <v>1</v>
+      </c>
       <c r="F14" s="30">
-        <v>45962</v>
+        <v>45976</v>
       </c>
       <c r="G14" s="30">
-        <v>46022</v>
+        <v>46006</v>
       </c>
       <c r="H14" s="24"/>
       <c r="I14" s="25"/>
@@ -1904,28 +1919,32 @@
       <c r="AQ14" s="23"/>
       <c r="AS14" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AT14" s="54">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AU14" s="56">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="3:47" ht="21" customHeight="1">
       <c r="C15" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="33"/>
-      <c r="E15" s="26"/>
+        <v>37</v>
+      </c>
+      <c r="D15" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="27">
+        <v>1</v>
+      </c>
       <c r="F15" s="30">
-        <v>45962</v>
+        <v>45977</v>
       </c>
       <c r="G15" s="30">
-        <v>46022</v>
+        <v>45981</v>
       </c>
       <c r="H15" s="24"/>
       <c r="I15" s="25"/>
@@ -1965,28 +1984,32 @@
       <c r="AQ15" s="23"/>
       <c r="AS15" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AT15" s="54">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AU15" s="56">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="3:47" ht="21" customHeight="1">
       <c r="C16" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="33"/>
-      <c r="E16" s="26"/>
+        <v>38</v>
+      </c>
+      <c r="D16" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="27">
+        <v>0.6</v>
+      </c>
       <c r="F16" s="30">
-        <v>45962</v>
+        <v>45983</v>
       </c>
       <c r="G16" s="30">
-        <v>46022</v>
+        <v>46081</v>
       </c>
       <c r="H16" s="24"/>
       <c r="I16" s="25"/>
@@ -2026,20 +2049,20 @@
       <c r="AQ16" s="23"/>
       <c r="AS16" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AT16" s="54">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AU16" s="56">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>630</v>
       </c>
     </row>
     <row r="17" spans="3:47" ht="25" customHeight="1">
       <c r="C17" s="35" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D17" s="35"/>
       <c r="E17" s="31"/>
@@ -2096,15 +2119,19 @@
     </row>
     <row r="18" spans="3:47" ht="21" customHeight="1">
       <c r="C18" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="33"/>
-      <c r="E18" s="26"/>
+        <v>42</v>
+      </c>
+      <c r="D18" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="27">
+        <v>0</v>
+      </c>
       <c r="F18" s="30">
-        <v>45945</v>
+        <v>46104</v>
       </c>
       <c r="G18" s="30">
-        <v>46022</v>
+        <v>46104</v>
       </c>
       <c r="H18" s="24"/>
       <c r="I18" s="25"/>
@@ -2144,29 +2171,25 @@
       <c r="AQ18" s="23"/>
       <c r="AS18" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AT18" s="54">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AU18" s="56">
         <f t="shared" si="2"/>
-        <v>495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="3:47" ht="21" customHeight="1">
       <c r="C19" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="30">
-        <v>45962</v>
-      </c>
-      <c r="G19" s="30">
-        <v>46022</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
       <c r="H19" s="24"/>
       <c r="I19" s="25"/>
       <c r="J19" s="25"/>
@@ -2205,29 +2228,25 @@
       <c r="AQ19" s="23"/>
       <c r="AS19" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AT19" s="54">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AU19" s="56">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="3:47" ht="21" customHeight="1">
       <c r="C20" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="33"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="30">
-        <v>45962</v>
-      </c>
-      <c r="G20" s="30">
-        <v>46022</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
       <c r="H20" s="24"/>
       <c r="I20" s="25"/>
       <c r="J20" s="25"/>
@@ -2266,29 +2285,25 @@
       <c r="AQ20" s="23"/>
       <c r="AS20" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AT20" s="54">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AU20" s="56">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:47" ht="21" customHeight="1">
       <c r="C21" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="30">
-        <v>45962</v>
-      </c>
-      <c r="G21" s="30">
-        <v>46022</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
       <c r="H21" s="24"/>
       <c r="I21" s="25"/>
       <c r="J21" s="25"/>
@@ -2327,20 +2342,20 @@
       <c r="AQ21" s="23"/>
       <c r="AS21" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AT21" s="54">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AU21" s="56">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="3:47" ht="25" customHeight="1">
       <c r="C22" s="35" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D22" s="35"/>
       <c r="E22" s="31"/>
@@ -2397,16 +2412,12 @@
     </row>
     <row r="23" spans="3:47" ht="21" customHeight="1">
       <c r="C23" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="33"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="30">
-        <v>45945</v>
-      </c>
-      <c r="G23" s="30">
-        <v>46022</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
       <c r="H23" s="24"/>
       <c r="I23" s="25"/>
       <c r="J23" s="25"/>
@@ -2445,29 +2456,25 @@
       <c r="AQ23" s="23"/>
       <c r="AS23" s="8">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AT23" s="54">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AU23" s="56">
         <f t="shared" si="2"/>
-        <v>495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="3:47" ht="21" customHeight="1">
       <c r="C24" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="33"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="30">
-        <v>45962</v>
-      </c>
-      <c r="G24" s="30">
-        <v>46022</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
       <c r="H24" s="24"/>
       <c r="I24" s="25"/>
       <c r="J24" s="25"/>
@@ -2506,29 +2513,25 @@
       <c r="AQ24" s="23"/>
       <c r="AS24" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AT24" s="54">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AU24" s="56">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="3:47" ht="21" customHeight="1">
       <c r="C25" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="33"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="30">
-        <v>45962</v>
-      </c>
-      <c r="G25" s="30">
-        <v>46022</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
       <c r="H25" s="24"/>
       <c r="I25" s="25"/>
       <c r="J25" s="25"/>
@@ -2567,29 +2570,25 @@
       <c r="AQ25" s="23"/>
       <c r="AS25" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AT25" s="54">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AU25" s="56">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="3:47" ht="21" customHeight="1">
       <c r="C26" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="33"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="30">
-        <v>45962</v>
-      </c>
-      <c r="G26" s="30">
-        <v>46022</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
       <c r="H26" s="24"/>
       <c r="I26" s="25"/>
       <c r="J26" s="25"/>
@@ -2628,15 +2627,15 @@
       <c r="AQ26" s="23"/>
       <c r="AS26" s="8">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AT26" s="54">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AU26" s="56">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="3:47">
@@ -2660,45 +2659,45 @@
     </row>
     <row r="30" spans="3:47" ht="19.5">
       <c r="C30" s="46" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E30" s="63" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F30" s="64"/>
       <c r="AS30" s="52">
         <f>SUM(AS8:AS26)</f>
-        <v>148</v>
+        <v>18</v>
       </c>
       <c r="AT30" s="55">
         <f>SUM(AT8:AT26)</f>
-        <v>444</v>
+        <v>54</v>
       </c>
       <c r="AU30" s="57">
         <f>SUM(AU8:AU26)</f>
-        <v>6660</v>
+        <v>810</v>
       </c>
     </row>
     <row r="31" spans="3:47">
       <c r="C31" s="43"/>
       <c r="D31" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E31" s="63" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F31" s="64"/>
     </row>
     <row r="32" spans="3:47">
       <c r="C32" s="43"/>
       <c r="D32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="1"/>
-      <c r="F32" s="42"/>
+        <v>20</v>
+      </c>
+      <c r="E32" s="63"/>
+      <c r="F32" s="64"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
@@ -2706,10 +2705,10 @@
     <row r="33" spans="3:12">
       <c r="C33" s="43"/>
       <c r="D33" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33" s="1"/>
-      <c r="F33" s="42"/>
+        <v>24</v>
+      </c>
+      <c r="E33" s="63"/>
+      <c r="F33" s="64"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
@@ -2734,13 +2733,13 @@
     </row>
     <row r="36" spans="3:12">
       <c r="C36" s="51" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D36" s="47">
         <v>3</v>
       </c>
       <c r="E36" s="38" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F36" s="42"/>
       <c r="J36" s="2"/>
@@ -2749,13 +2748,13 @@
     </row>
     <row r="37" spans="3:12">
       <c r="C37" s="51" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D37" s="47">
         <v>15</v>
       </c>
       <c r="E37" s="38" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F37" s="42"/>
       <c r="J37" s="2"/>
@@ -2764,13 +2763,13 @@
     </row>
     <row r="38" spans="3:12">
       <c r="C38" s="51" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D38">
         <v>25</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F38" s="48"/>
     </row>
@@ -2781,9 +2780,11 @@
       <c r="F39" s="45"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="V3:Y3"/>
     <mergeCell ref="Z3:AC3"/>

--- a/docs/fattibilità/Gantt.xlsx
+++ b/docs/fattibilità/Gantt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gcomi\Desktop\psyPlatform\docs\fattibilità\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853E4104-3F99-4B5B-AF5E-E737FC75ED0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364FDE2F-3D44-469C-9E95-3540528E4FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9327F8D6-4F37-4E25-8083-20A17765DC2F}"/>
   </bookViews>
@@ -169,9 +169,6 @@
     <t>A, B</t>
   </si>
   <si>
-    <t xml:space="preserve">  Zoom con fisioterapista</t>
-  </si>
-  <si>
     <t>A,B</t>
   </si>
   <si>
@@ -179,6 +176,9 @@
   </si>
   <si>
     <t>Simone Scainelli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Zoom con psicologo</t>
   </si>
 </sst>
 </file>
@@ -650,29 +650,29 @@
     <xf numFmtId="166" fontId="0" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1069,10 +1069,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:47" ht="27" customHeight="1">
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="62"/>
+      <c r="D2" s="65"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="3:47">
@@ -1083,64 +1083,64 @@
       <c r="H3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="58" t="str">
+      <c r="I3" s="62" t="str">
         <f>TEXT(I5,"MMM")</f>
         <v>Oct</v>
       </c>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="58" t="str">
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="62" t="str">
         <f>TEXT(M5,"MMM")</f>
         <v>Nov</v>
       </c>
-      <c r="N3" s="59"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="58" t="str">
+      <c r="N3" s="63"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="64"/>
+      <c r="Q3" s="62" t="str">
         <f>TEXT(Q5,"MMM")</f>
         <v>Dec</v>
       </c>
-      <c r="R3" s="59"/>
-      <c r="S3" s="59"/>
-      <c r="T3" s="59"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
       <c r="U3" s="7"/>
-      <c r="V3" s="58" t="str">
+      <c r="V3" s="62" t="str">
         <f>TEXT(V5,"MMM")</f>
         <v>Jan</v>
       </c>
-      <c r="W3" s="59"/>
-      <c r="X3" s="59"/>
-      <c r="Y3" s="60"/>
-      <c r="Z3" s="58" t="str">
+      <c r="W3" s="63"/>
+      <c r="X3" s="63"/>
+      <c r="Y3" s="64"/>
+      <c r="Z3" s="62" t="str">
         <f>TEXT(Z5,"MMM")</f>
         <v>Feb</v>
       </c>
-      <c r="AA3" s="59"/>
-      <c r="AB3" s="59"/>
-      <c r="AC3" s="60"/>
-      <c r="AD3" s="58" t="str">
+      <c r="AA3" s="63"/>
+      <c r="AB3" s="63"/>
+      <c r="AC3" s="64"/>
+      <c r="AD3" s="62" t="str">
         <f>TEXT(AD5,"MMM")</f>
         <v>Mar</v>
       </c>
-      <c r="AE3" s="59"/>
-      <c r="AF3" s="59"/>
-      <c r="AG3" s="59"/>
+      <c r="AE3" s="63"/>
+      <c r="AF3" s="63"/>
+      <c r="AG3" s="63"/>
       <c r="AH3" s="7"/>
-      <c r="AI3" s="58" t="str">
+      <c r="AI3" s="62" t="str">
         <f>TEXT(AI5,"MMM")</f>
         <v>Apr</v>
       </c>
-      <c r="AJ3" s="59"/>
-      <c r="AK3" s="59"/>
-      <c r="AL3" s="60"/>
-      <c r="AM3" s="58" t="str">
+      <c r="AJ3" s="63"/>
+      <c r="AK3" s="63"/>
+      <c r="AL3" s="64"/>
+      <c r="AM3" s="62" t="str">
         <f>TEXT(AM5,"MMM")</f>
         <v>May</v>
       </c>
-      <c r="AN3" s="59"/>
-      <c r="AO3" s="59"/>
-      <c r="AP3" s="60"/>
+      <c r="AN3" s="63"/>
+      <c r="AO3" s="63"/>
+      <c r="AP3" s="64"/>
       <c r="AQ3" s="6" t="str">
         <f>TEXT(AQ5,"MMM")</f>
         <v>Jun</v>
@@ -1486,7 +1486,7 @@
       <c r="C8" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="65" t="s">
+      <c r="D8" s="58" t="s">
         <v>41</v>
       </c>
       <c r="E8" s="27">
@@ -1554,7 +1554,7 @@
       <c r="C9" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="65" t="s">
+      <c r="D9" s="58" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="27">
@@ -1619,7 +1619,7 @@
       <c r="C10" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="65" t="s">
+      <c r="D10" s="58" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="27">
@@ -1684,7 +1684,7 @@
       <c r="C11" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="65" t="s">
+      <c r="D11" s="58" t="s">
         <v>20</v>
       </c>
       <c r="E11" s="27"/>
@@ -1804,7 +1804,7 @@
       <c r="C13" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="65" t="s">
+      <c r="D13" s="58" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="27">
@@ -1869,7 +1869,7 @@
       <c r="C14" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="65" t="s">
+      <c r="D14" s="58" t="s">
         <v>19</v>
       </c>
       <c r="E14" s="27">
@@ -1934,7 +1934,7 @@
       <c r="C15" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="65" t="s">
+      <c r="D15" s="58" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="27">
@@ -1999,7 +1999,7 @@
       <c r="C16" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="65" t="s">
+      <c r="D16" s="58" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="27">
@@ -2119,10 +2119,10 @@
     </row>
     <row r="18" spans="3:47" ht="21" customHeight="1">
       <c r="C18" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="58" t="s">
         <v>42</v>
-      </c>
-      <c r="D18" s="65" t="s">
-        <v>43</v>
       </c>
       <c r="E18" s="27">
         <v>0</v>
@@ -2186,8 +2186,8 @@
       <c r="C19" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
       <c r="F19" s="30"/>
       <c r="G19" s="30"/>
       <c r="H19" s="24"/>
@@ -2243,8 +2243,8 @@
       <c r="C20" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="65"/>
-      <c r="E20" s="65"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
       <c r="F20" s="30"/>
       <c r="G20" s="30"/>
       <c r="H20" s="24"/>
@@ -2300,8 +2300,8 @@
       <c r="C21" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
       <c r="F21" s="30"/>
       <c r="G21" s="30"/>
       <c r="H21" s="24"/>
@@ -2414,8 +2414,8 @@
       <c r="C23" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
       <c r="F23" s="30"/>
       <c r="G23" s="30"/>
       <c r="H23" s="24"/>
@@ -2471,8 +2471,8 @@
       <c r="C24" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="65"/>
-      <c r="E24" s="65"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
       <c r="F24" s="30"/>
       <c r="G24" s="30"/>
       <c r="H24" s="24"/>
@@ -2528,8 +2528,8 @@
       <c r="C25" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
       <c r="F25" s="30"/>
       <c r="G25" s="30"/>
       <c r="H25" s="24"/>
@@ -2585,8 +2585,8 @@
       <c r="C26" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
       <c r="F26" s="30"/>
       <c r="G26" s="30"/>
       <c r="H26" s="24"/>
@@ -2664,10 +2664,10 @@
       <c r="D30" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="64"/>
+      <c r="E30" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="60"/>
       <c r="AS30" s="52">
         <f>SUM(AS8:AS26)</f>
         <v>18</v>
@@ -2686,18 +2686,18 @@
       <c r="D31" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E31" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31" s="64"/>
+      <c r="E31" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" s="60"/>
     </row>
     <row r="32" spans="3:47">
       <c r="C32" s="43"/>
       <c r="D32" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E32" s="63"/>
-      <c r="F32" s="64"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="60"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
@@ -2707,8 +2707,8 @@
       <c r="D33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E33" s="63"/>
-      <c r="F33" s="64"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="60"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
@@ -2781,11 +2781,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="C3:D3"/>
     <mergeCell ref="V3:Y3"/>
     <mergeCell ref="Z3:AC3"/>
     <mergeCell ref="C2:D2"/>
@@ -2795,6 +2790,11 @@
     <mergeCell ref="M3:P3"/>
     <mergeCell ref="Q3:T3"/>
     <mergeCell ref="AD3:AG3"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="C3:D3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="E8:E26">
@@ -2811,12 +2811,12 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:AP8 I9:AP11 I13:V26 Y13:AD26 AG13:AL26 AO13:AP26">
+  <conditionalFormatting sqref="H8:AP8 I9:AP11 I13:V26 Y13:AD26 AG13:AL26 AO13:AP26 W16:X16">
     <cfRule type="expression" dxfId="2" priority="10">
       <formula>AND(H$5&gt;=$F8,H$5&lt;=$G8)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8:AP8 I9:AP26 I5:AQ7 AQ8:AQ26">
+  <conditionalFormatting sqref="H8:AP8 I5:AQ7 AQ8:AQ26 I9:AP26">
     <cfRule type="expression" dxfId="1" priority="13">
       <formula>AND(H$5&lt;=TODAY(), (I$5-7)&lt;=TODAY(),I$5&gt;=TODAY())</formula>
     </cfRule>
